--- a/data/AREA_OPERACIONAL.xlsx
+++ b/data/AREA_OPERACIONAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gflopes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9266E3B3-DC70-4A3E-881D-5DCD1BD0DEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7CF277-8E78-457F-9B84-54CAB80A3A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARÉAS OPERACIONAL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="316">
   <si>
     <t>Região</t>
   </si>
@@ -975,9 +975,6 @@
   </si>
   <si>
     <t>REGIANE INAMORATO</t>
-  </si>
-  <si>
-    <t>ROBSON ANDRE</t>
   </si>
   <si>
     <t>01001-000</t>
@@ -1016,7 +1013,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1032,6 +1029,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1135,7 +1138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1179,6 +1182,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1529,7 +1535,7 @@
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>271</v>
@@ -1656,8 +1662,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>313</v>
+      <c r="A9" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>132</v>
@@ -1676,8 +1682,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>313</v>
+      <c r="A10" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>132</v>
@@ -1696,8 +1702,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>313</v>
+      <c r="A11" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>132</v>
@@ -1716,8 +1722,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>313</v>
+      <c r="A12" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>132</v>
@@ -2533,7 +2539,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>3</v>
@@ -2551,7 +2557,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>3</v>
@@ -2569,7 +2575,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>3</v>
@@ -2587,7 +2593,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>3</v>
@@ -2767,7 +2773,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>3</v>
@@ -2785,7 +2791,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>3</v>
@@ -2803,7 +2809,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>3</v>
@@ -2821,7 +2827,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>3</v>
@@ -2839,7 +2845,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>3</v>
@@ -2983,7 +2989,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>3</v>
@@ -3055,7 +3061,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>3</v>
@@ -3091,7 +3097,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>3</v>
@@ -3127,7 +3133,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>3</v>
@@ -3200,6 +3206,29 @@
   </sheetData>
   <autoFilter ref="A1:F89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="39">
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C70:D70"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C56:D56"/>
     <mergeCell ref="C51:D51"/>
@@ -3216,29 +3245,6 @@
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
